--- a/tiflow-core/develop/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T05:36:09+00:00</t>
+    <t>2026-04-14T09:43:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-core/develop/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T09:43:07+00:00</t>
+    <t>2026-04-15T07:27:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-core/develop/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:27:24+00:00</t>
+    <t>2026-04-16T13:59:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-core/develop/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T13:59:19+00:00</t>
+    <t>2026-04-16T14:10:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-core/develop/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T14:10:44+00:00</t>
+    <t>2026-04-20T12:14:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-core/develop/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T12:14:42+00:00</t>
+    <t>2026-04-27T11:44:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-core/develop/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-27T11:44:41+00:00</t>
+    <t>2026-04-30T06:20:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-core/develop/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T06:20:35+00:00</t>
+    <t>2026-05-06T21:45:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-core/develop/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T21:45:27+00:00</t>
+    <t>2026-05-07T11:05:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-core/develop/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T11:05:45+00:00</t>
+    <t>2026-05-08T13:19:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-core/develop/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T13:19:09+00:00</t>
+    <t>2026-05-08T22:34:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-core/develop/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T22:34:08+00:00</t>
+    <t>2026-05-12T09:57:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-core/develop/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T09:57:56+00:00</t>
+    <t>2026-05-12T14:25:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-core/develop/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T14:25:24+00:00</t>
+    <t>2026-05-15T11:15:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-core/develop/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T11:15:10+00:00</t>
+    <t>2026-05-18T04:37:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-core/develop/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T04:37:27+00:00</t>
+    <t>2026-05-19T15:16:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
